--- a/data/data_replicated/3p_nomod_sFRiman/traces_references.xlsx
+++ b/data/data_replicated/3p_nomod_sFRiman/traces_references.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <si>
     <t xml:space="preserve">trace</t>
   </si>
@@ -20,7 +20,7 @@
     <t xml:space="preserve">reference</t>
   </si>
   <si>
-    <t xml:space="preserve">c29-c49-c50-29d2e-49d3e-50d3I15-05-025-05-20402-20503-86652.csv</t>
+    <t xml:space="preserve">c29-c49-c50-29d3S30-49d3S10-50d2S30-00078-00156-00625-602-860-2438.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c29</t>
@@ -32,22 +32,16 @@
     <t xml:space="preserve">c50</t>
   </si>
   <si>
-    <t xml:space="preserve">c29-c49-c50-29d3S30-49d3S10-50d2S30-00078-00156-00625-602-860-2438.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c29-c49-c50-29d3S30-49d3S10-50d3I15-0125-012-025-10659-10877-43914.csv</t>
+    <t xml:space="preserve">c29-c49-c50-29d3a-49d4a-50d3a-00625-00156-0125-9973-11722-38721.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c29-c49-c50-29d3a-49d4a-50d4a-00078-00078-00156-1324-4732-5823.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c29-c49-c50-29d3a-49d4a-50d4a-00625-00156-016-9973-11722-67760.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c29-c49-c50-29d3c-49d3e-50d3I15-025-025-05-18629-20503-86652.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c29-c49-c50-29d3c-49d4I35-50d2S30-00078-00156-0125-1274-1595-5270.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c29-c49-c50-29d3d-49d4I35-50d3c-00625-003125-00625-3748-4196-17497.csv</t>
+    <t xml:space="preserve">c29-c49-c50-29d3a-49d4a-50d4a-00625-003125-016-9973-17970-67760.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c29-c49-c50-29d3d-49d4d-50d3c-00625-003125-00625-3748-4343-17497.csv</t>
@@ -65,7 +59,7 @@
     <t xml:space="preserve">c29-c49-c50-29d4I22-49d4I15-50d3I15-003125-00625-025-9433-12242-43914.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c30-c31-c32-30d2c-31d1U105-32d2U15-025-05-05-26181-74585-115291.csv</t>
+    <t xml:space="preserve">c30-c31-c32-30d2e-31d3a-32d3a-0125-00625-00625-6876-29248-31167.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c30</t>
@@ -77,31 +71,28 @@
     <t xml:space="preserve">c32</t>
   </si>
   <si>
-    <t xml:space="preserve">c30-c31-c32-30d2e-31d2U15-32d3-0125-05-30-6876-29698-30221.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c30-c31-c32-30d3S2-31d2S10-32d1S30-003125-0125-025-7115-26260-31687.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c30-c31-c32-30d3S2-31d3S10-32d3S30-00078-003125-00625-1731-5068-6472.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c30-c31-c32-30d3a-31d1U105-32d2U15-0125-05-05-28624-74585-115291.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c30-c31-c32-30d3a-31d2U15-32d2U105-003125-05-025-6845-29698-41732.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c30-c31-c32-30d3a-31d2U60-32d2U60-00156-025-0125-3208-13581-19568.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c30-c31-c32-30d3a-31d3a-32d3a-003125-00625-00625-6845-29248-31167.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c30-c31-c32-30d3c-31d2S10-32d3I35-0125-025-0125-12116-47246-47553.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c30-c31-c32-30d3c-31d2U15-32d2U105-00625-05-025-8742-29698-41732.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c30-c31-c32-30d3e-31d2-32d2U105-014-15-0125-4896-19405-20631.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c30-c31-c32-30d3e-31d2U60-32d2U60-014-025-0125-4896-13581-19568.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c30-c31-c32-30d4I15-31d2U15-32d2U105-003125-05-025-9776-29698-41732.csv</t>
+    <t xml:space="preserve">c30-c31-c32-30d3c-31d3a-32d3a-00625-00625-00625-8742-29248-31167.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c30-c31-c32-30d3c-31d3a-32d3a-0125-0125-0125-12116-52403-64824.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c30-c31-c32-30d4I15-31d4I22-32d2I22-003125-0125-0125-9776-44706-51305.csv</t>
@@ -116,40 +107,34 @@
     <t xml:space="preserve">c30-c31-c32-30d4I35-31d4I15-32d4I35-00156-003125-00625-4730-16223-21257.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c30-c32-c31-30d3I35-32d2U60-31d1U105-00625-05-05-15990-67153-74585.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c30-c32-c31-30d3S2-32d3S30-31d3S10-00156-009-011-2648-9643-15824.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c30-c32-c31-30d3S2-32d3U60-31d3U15-00078-00625-0125-1731-6205-6313.csv</t>
+    <t xml:space="preserve">c30-c32-c31-30d3a-32d2U105-31d3U15-00156-00625-025-3208-11065-11959.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c30-c32-c31-30d3a-32d2U60-31d1U105-00625-05-05-14556-67153-74585.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c30-c32-c31-30d3a-32d2a-31d2a-0125-025-025-28624-103678-111976.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c30-c32-c31-30d3a-32d3U60-31d3U15-00078-00625-0125-2217-6205-6313.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c30-c32-c31-30d3a-32d3a-31d3a-00156-003125-003125-3208-10650-11425.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c30-c32-c31-30d3c-32d1S30-31d4I15-00625-025-00625-8742-31687-32799.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c30-c32-c31-30d3d-32d3S30-31d4I15-00156-00625-00156-1532-6472-6649.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c30-c32-c31-30d3d-32d3U60-31d3U60-00156-00625-0125-1532-6205-6283.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c30-c32-c31-30d3d-32d4I15-31d3S10-00625-003125-011-3798-14272-15824.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c30-c32-c31-30d3e-32d2U105-31d3U15-00625-00625-025-2703-11065-11959.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c30-c32-c31-30d3e-32d3S30-31d2S10-00625-009-00625-2703-9643-10549.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c30-c32-c31-30d4I15-32d2U60-31d1U105-00625-05-05-19213-67153-74585.csv</t>
+    <t xml:space="preserve">c30-c32-c31-30d3d-32d3a-31d3a-00156-00156-00156-1532-6213-6584.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c30-c32-c31-30d3d-32d3a-31d3a-00625-003125-003125-3798-10650-11425.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c30-c32-c31-30d3e-32d3a-31d3a-00625-003125-003125-2703-10650-11425.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c30-c32-c31-30d3e-32d3a-31d3a-014-003125-00625-4896-10650-29248.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c30-c32-c31-30d4I15-32d4I35-31d4I22-00156-00625-00625-5247-21257-23829.csv</t>
@@ -164,7 +149,7 @@
     <t xml:space="preserve">c30-c32-c31-30d4I22-32d4I22-31d4I35-00156-00156-003125-4196-7266-7632.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c36-c38-c37-36d1-38d2-37d4I35-45-15-00625-10167-10893-19462.csv</t>
+    <t xml:space="preserve">c36-c38-c37-36d3a-38d3a-37d2a-0125-0125-025-22142-27797-68907.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c36</t>
@@ -176,16 +161,16 @@
     <t xml:space="preserve">c38</t>
   </si>
   <si>
-    <t xml:space="preserve">c36-c38-c37-36d3-38d3-37d4I35-15-15-00156-1930-2315-4687.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c36-c38-c37-36d3-38d3S30-37d2S10-15-007-00625-6057-6155-12100.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c36-c38-c37-36d3-38d3S30-37d3-15-00156-45-1930-2275-4445.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c36-c38-c37-36d3a-38d3a-37d2a-0125-0125-025-22142-27797-68907.csv</t>
+    <t xml:space="preserve">c36-c38-c37-36d3a-38d3a-37d3a-00078-00078-00078-1251-2135-2793.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c36-c38-c37-36d3a-38d3a-37d3a-00156-00078-00078-1860-2135-2793.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c36-c38-c37-36d3a-38d3a-37d3a-00156-00078-00156-1860-2135-5376.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c36-c38-c37-36d3a-38d3a-37d3a-003125-00156-003125-2719-4218-8324.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c36-c38-c37-36d3a-38d3a-37d3a-00625-00625-00625-8275-15325-21031.csv</t>
@@ -194,34 +179,19 @@
     <t xml:space="preserve">c36-c38-c37-36d3a-38d3a-37d3a-0125-0125-0125-22142-27797-31376.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c36-c38-c37-36d4I22-38d4I35-37d4I22-003125-003125-00625-8409-9093-17284.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c36-c38-c37-36d4I35-38d3I35-37d2S10-0125-0125-025-26661-29794-51848.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c38-c36-c37-38d2-36d2-37d1-45-45-30-1573-1604-3070.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c38-c36-c37-38d2-36d3S2-37d3I35-15-00625-0125-18945-18968-38842.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c38-c36-c37-38d2-36d4I15-37d4I15-15-003125-00625-10893-11311-23718.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c38-c36-c37-38d3-36d2-37d1-15-45-30-3809-4386-7482.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c38-c36-c37-38d3S30-36d2-37d3-00078-45-15-1176-1604-2408.csv</t>
+    <t xml:space="preserve">c38-c36-c37-38d3a-36d3a-37d3a-00078-003125-00156-2135-2719-5376.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c38-c36-c37-38d3a-36d3a-37d3a-003125-00625-003125-7130-8275-8324.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c38-c36-c37-38d4I22-36d4I35-37d2-00625-00625-15-15445-15874-33117.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c41-c43-c42-41d3-43d3U15-42d2S2-30-00625-025-7600-7676-68570.csv</t>
+    <t xml:space="preserve">c38-c36-c37-38d3a-36d3a-37d3a-003125-00625-00625-7130-8275-21031.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c38-c36-c37-38d3a-36d3a-37d3a-00625-0125-0125-15325-22142-31376.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c41-c43-c42-41d3a-43d3a-42d2a-00625-00625-05-23585-31591-189293.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c41</t>
@@ -233,46 +203,28 @@
     <t xml:space="preserve">c43</t>
   </si>
   <si>
-    <t xml:space="preserve">c41-c43-c42-41d3-43d3U15-42d4I15-45-00313-00625-2568-2669-25017.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c41-c43-c42-41d3-43d4I15-42d3I35-45-003125-0125-4382-4584-36452.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c41-c43-c42-41d3-43d4I15-42d4I35-45-00156-00625-2568-2658-22693.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c41-c43-c42-41d3S30-43d2-42d3U15-00156-45-025-1695-1706-15081.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c41-c43-c42-41d3a-43d3a-42d2a-00625-00625-05-23585-31591-189293.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c41-c43-c42-41d3a-43d3a-42d3a-00078-00156-0125-4856-5674-49447.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c41-c43-c42-41d4I22-43d2-42d4I22-00156-45-0125-5433-5482-48899.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c43-c41-c42-43d2-41d3S30-42d3S2-45-003125-0125-3162-3611-26116.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c43-c41-c42-43d3-41d3-42d4I22-30-45-00625-2082-2568-20605.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c43-c41-c42-43d3-41d3U105-42d3-30-0125-15-6427-6429-53025.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c43-c41-c42-43d3a-41d3a-42d2a-003125-00625-05-10202-23585-189293.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c43-c41-c42-43d3a-41d3a-42d3a-00078-00078-003125-2722-4856-11970.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c43-c41-c42-43d3a-41d3a-42d3a-00078-00078-00625-2722-4856-22419.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c43-c41-c42-43d3a-41d3a-42d3a-00156-00156-0125-5674-7630-49447.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c43-c41-c42-43d3a-41d3a-42d3a-00156-00156-025-5674-7630-79251.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c43-c41-c42-43d3a-41d3a-42d3a-003125-003125-025-10202-10975-79251.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c43-c41-c42-43d4I35-41d3U105-42d3I22-00625-025-025-11159-11468-102118.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c44-c45-c46-44d3-45d3-46d3-15-30-15-4636-8847-9273.csv</t>
+    <t xml:space="preserve">c44-c45-c46-44d3a-45d3a-46d3a-00078-00156-00156-3347-5175-5843.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c44</t>
@@ -284,52 +236,31 @@
     <t xml:space="preserve">c46</t>
   </si>
   <si>
-    <t xml:space="preserve">c44-c45-c46-44d3-45d4I22-46d3-45-003125-30-3148-5717-6107.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c44-c45-c46-44d3-45d4I35-46d3-30-00156-15-1816-4191-4357.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c44-c45-c46-44d3S30-45d3-46d2-00156-30-45-1458-2764-2903.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c44-c45-c46-44d3S30-45d4I35-46d4I22-003125-003125-003125-2662-4992-5617.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c44-c45-c46-44d3a-45d3a-46d3a-003125-003125-00625-10346-13722-32504.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c44-c45-c46-44d4I22-45d2-46d2-003125-30-30-6170-12289-12714.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c44-c45-c46-44d4I35-45d4I22-46d4I35-00156-003125-003125-2947-5717-5919.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c44-c46-c45-44d2-46d2-45d2-45-15-15-18364-37443-39752.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c44-c46-c45-44d2-46d2-45d4I15-45-30-0125-12555-24204-25277.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c44-c46-c45-44d3-46d4I15-45d3-30-00156-15-1816-3414-3795.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c44-c46-c45-44d3a-46d3a-45d3a-00156-003125-003125-5690-12014-13722.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c44-c46-c45-44d3a-46d3a-45d3a-003125-003125-003125-10346-12014-13722.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c44-c46-c45-44d3a-46d3a-45d3a-00625-00625-0125-23280-32504-50820.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c44-c46-c45-44d3a-46d3a-45d3a-00625-0125-0125-23280-48592-50820.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c44-c46-c45-44d3a-46d3a-45d3a-0125-0125-0125-45891-48592-50820.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c44-c46-c45-44d4I15-46d4I15-45d3-00156-003125-30-4257-8768-8847.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c44-c46-c45-44d4I35-46d4I22-45d4I22-00625-0125-0125-10225-20621-20858.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c46-c47-c48-46d3-47d2S30-48d2d-15-0125-0125-18506-18570-19587.csv</t>
+    <t xml:space="preserve">c45-c44-c46-45d3a-44d3a-46d3a-00156-00156-003125-5175-5690-12014.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c46-c45-c44-46d3a-45d3a-44d3a-00078-00078-00078-2525-3180-3347.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c46-c47-c48-46d3a-47d3a-48d2d-003125-003125-0125-12014-13868-19587.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c47</t>
@@ -338,76 +269,52 @@
     <t xml:space="preserve">c48</t>
   </si>
   <si>
+    <t xml:space="preserve">c46-c47-c48-46d3a-47d3a-48d2e-00156-00156-0125-5843-7319-7809.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c46-c47-c48-46d3a-47d3a-48d4a-00078-00078-00078-2525-3912-5468.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c46-c47-c48-46d3a-47d3a-48d4a-00156-00156-00156-5843-7319-7889.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c46-c48-c47-46d2-48d2e-47d4I22-45-0125-003125-7099-7809-8047.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c46-c48-c47-46d3-48d3c-47d3-15-00625-30-9273-9455-9588.csv</t>
+    <t xml:space="preserve">c46-c48-c47-46d3a-48d4d-47d3a-00078-00156-00078-2525-3507-3912.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c46-c48-c47-46d3a-48d4e-47d3a-00078-00156-00078-2525-2536-3912.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c46-c48-c47-46d4I15-48d4I35-47d4I22-00156-00156-00156-3414-3553-3908.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c46-c48-c47-46d4I15-48d4d-47d4I22-00156-00156-00156-3414-3507-3908.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c46-c48-c47-46d4I35-48d4I22-47d4I22-00156-00156-00156-2987-3132-3908.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c47-c46-c48-47d3-46d1-48d2S2-15-45-00625-11384-14174-14465.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c47-c46-c48-47d4I35-46d3-48d2d-00625-15-0125-18268-18506-19587.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c47-c48-c46-47d2S30-48d3S2-46d3S10-00625-003125-009-9172-10617-13315.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c47-c48-c46-47d3-48d4I35-46d4I22-30-003125-003125-5416-5491-5617.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c47-c48-c46-47d3-48d4e-46d3-45-00078-30-1697-1770-1968.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c47-c48-c46-47d3S30-48d3d-46d4I15-007-00625-003125-8072-8635-8768.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c47-c48-c46-47d3a-48d3a-46d3a-00625-0125-0125-36901-45104-48592.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c47-c48-c46-47d3a-48d4a-46d3a-00078-00078-00156-3912-5468-5843.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c47-c48-c46-47d3a-48d4a-46d3a-00156-00156-003125-7319-7889-12014.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c47-c48-c46-47d3a-48d4c-46d3a-00078-00156-00156-3912-4505-5843.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c47-c48-c46-47d4I15-48d4I35-46d4I22-00156-003125-003125-4491-5491-5617.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c47-c48-c46-47d4I15-48d4c-46d3-00156-00156-45-4491-4505-4565.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c47-c48-c46-47d4I35-48d4I15-46d4I22-00625-0125-0125-18268-20060-20621.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c47-c48-c46-47d4I35-48d4I35-46d4I15-003125-00625-00625-8836-13556-14456.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c47-c48-c49-47d3-48d2d-49d3e-30-0125-025-2378-19587-20503.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c47-c48-c49-47d3-48d2d-49d3e-45-0125-025-2764-19587-20503.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c47-c48-c49-47d3-48d4c-49d2d-15-016-0125-3130-31010-36100.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c47-c48-c49-47d3-48d4d-49d3e-45-011-0125-1697-12530-15132.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c47-c48-c49-47d3-48d4d-49d4c-45-011-009-1697-12530-14373.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c47-c48-c49-47d3S30-48d4c-49d3d-00078-003125-00625-1197-11072-12210.csv</t>
+    <t xml:space="preserve">c47-c48-c49-47d3a-48d2d-49d3e-00078-0125-025-3912-19587-20503.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c47-c48-c49-47d3a-48d3a-49d3a-00156-0125-0125-7319-45104-52456.csv</t>
@@ -416,21 +323,30 @@
     <t xml:space="preserve">c47-c48-c49-47d3a-48d4a-49d4a-00078-003125-00625-3912-43685-47080.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c47-c48-c49-47d4I22-48d4c-49d2d-00156-016-0125-3908-31010-36100.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c47-c49-c48-47d3-49d3c-48d2d-15-0125-025-3130-26442-30352.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c47-c49-c48-47d3-49d3c-48d2d-45-00625-0125-1697-15741-19587.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c47-c49-c48-47d3S30-49d3c-48d2c-00156-0125-0125-3040-26442-27592.csv</t>
+    <t xml:space="preserve">c47-c48-c49-47d3a-48d4c-49d2d-00078-016-0125-3912-31010-36100.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c47-c48-c49-47d3a-48d4c-49d3d-00078-003125-00625-3912-11072-12210.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c47-c48-c49-47d3a-48d4d-49d3e-00078-011-0125-3912-12530-15132.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c47-c48-c49-47d3a-48d4d-49d4c-00078-011-009-3912-12530-14373.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c47-c49-c48-47d3a-49d3a-48d2a-00156-025-025-7319-95649-105784.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c47-c49-c48-47d3a-49d3c-48d2c-00078-0125-0125-3912-26442-27592.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c47-c49-c48-47d3a-49d3c-48d2d-00078-00625-0125-3912-15741-19587.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c47-c49-c48-47d3a-49d3c-48d2d-00078-0125-025-3912-26442-30352.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c48-c46-c47-48d2S2-46d2S10-47d2S30-00625-00625-0125-14465-15039-18570.csv</t>
   </si>
   <si>
@@ -446,21 +362,15 @@
     <t xml:space="preserve">c48-c46-c47-48d4a-46d3a-47d3a-00156-003125-003125-7889-12014-13868.csv</t>
   </si>
   <si>
+    <t xml:space="preserve">c48-c46-c47-48d4e-46d3a-47d3a-00078-00078-00078-1770-2525-3912.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">c48-c47-c46-48d3S2-47d3S30-46d3S10-00078-00156-00156-2653-3040-3247.csv</t>
   </si>
   <si>
     <t xml:space="preserve">c48-c47-c46-48d4I15-47d4I22-46d4I15-003125-003125-003125-7513-8047-8768.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c48-c47-c46-48d4I15-47d4I22-46d4I22-0125-00625-0125-20060-20082-20621.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c48-c47-c46-48d4c-47d3-46d4I22-00156-30-003125-4505-5416-5617.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c48-c47-c46-48d4e-47d3-46d2-00156-45-45-2536-2764-2903.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c49-c29-c50-49d2S10-29d3S30-50d1S30-00625-00625-05-4795-5353-27636.csv</t>
   </si>
   <si>
@@ -470,12 +380,6 @@
     <t xml:space="preserve">c49-c29-c50-49d3S10-29d3S30-50d2S30-003125-003125-025-1967-2340-7818.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">c49-c29-c50-49d3S10-29d3e-50d4I22-00156-00156-003125-860-1039-4153.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c49-c29-c50-49d3c-29d2c-50d3I35-0125-05-05-26442-27715-104547.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">c49-c29-c50-49d3e-29d3d-50d2d-00625-027-025-8741-9048-34331.csv</t>
   </si>
   <si>
@@ -513,9 +417,6 @@
   </si>
   <si>
     <t xml:space="preserve">c49-c29-c50-49d4d-29d3e-50d4c-00078-003125-005-1953-2230-7994.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c49-c29-c50-49d4d-29d4I22-50d3c-003125-00156-00625-4343-4954-17497.csv</t>
   </si>
 </sst>
 </file>
@@ -1097,7 +998,7 @@
         <v>15</v>
       </c>
       <c r="B32" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
@@ -1105,7 +1006,7 @@
         <v>15</v>
       </c>
       <c r="B33" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34">
@@ -1113,55 +1014,55 @@
         <v>15</v>
       </c>
       <c r="B34" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" t="s">
         <v>16</v>
-      </c>
-      <c r="B35" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B36" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B37" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B38" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>20</v>
+      </c>
+      <c r="B39" t="s">
         <v>17</v>
-      </c>
-      <c r="B39" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41">
@@ -1169,7 +1070,7 @@
         <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
@@ -1177,7 +1078,7 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43">
@@ -1185,7 +1086,7 @@
         <v>21</v>
       </c>
       <c r="B43" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44">
@@ -1193,7 +1094,7 @@
         <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
@@ -1201,7 +1102,7 @@
         <v>22</v>
       </c>
       <c r="B45" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46">
@@ -1209,7 +1110,7 @@
         <v>22</v>
       </c>
       <c r="B46" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47">
@@ -1217,7 +1118,7 @@
         <v>23</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48">
@@ -1225,7 +1126,7 @@
         <v>23</v>
       </c>
       <c r="B48" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49">
@@ -1233,7 +1134,7 @@
         <v>23</v>
       </c>
       <c r="B49" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50">
@@ -1241,7 +1142,7 @@
         <v>24</v>
       </c>
       <c r="B50" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51">
@@ -1249,7 +1150,7 @@
         <v>24</v>
       </c>
       <c r="B51" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52">
@@ -1257,7 +1158,7 @@
         <v>24</v>
       </c>
       <c r="B52" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53">
@@ -1265,7 +1166,7 @@
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54">
@@ -1273,7 +1174,7 @@
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55">
@@ -1281,7 +1182,7 @@
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56">
@@ -1289,7 +1190,7 @@
         <v>26</v>
       </c>
       <c r="B56" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
@@ -1297,7 +1198,7 @@
         <v>26</v>
       </c>
       <c r="B57" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58">
@@ -1305,7 +1206,7 @@
         <v>26</v>
       </c>
       <c r="B58" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59">
@@ -1313,7 +1214,7 @@
         <v>27</v>
       </c>
       <c r="B59" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60">
@@ -1321,7 +1222,7 @@
         <v>27</v>
       </c>
       <c r="B60" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61">
@@ -1329,7 +1230,7 @@
         <v>27</v>
       </c>
       <c r="B61" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62">
@@ -1337,7 +1238,7 @@
         <v>28</v>
       </c>
       <c r="B62" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63">
@@ -1345,7 +1246,7 @@
         <v>28</v>
       </c>
       <c r="B63" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="64">
@@ -1353,7 +1254,7 @@
         <v>28</v>
       </c>
       <c r="B64" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65">
@@ -1361,7 +1262,7 @@
         <v>29</v>
       </c>
       <c r="B65" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66">
@@ -1369,7 +1270,7 @@
         <v>29</v>
       </c>
       <c r="B66" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67">
@@ -1377,7 +1278,7 @@
         <v>29</v>
       </c>
       <c r="B67" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="68">
@@ -1385,7 +1286,7 @@
         <v>30</v>
       </c>
       <c r="B68" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69">
@@ -1393,7 +1294,7 @@
         <v>30</v>
       </c>
       <c r="B69" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70">
@@ -1401,7 +1302,7 @@
         <v>30</v>
       </c>
       <c r="B70" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71">
@@ -1409,7 +1310,7 @@
         <v>31</v>
       </c>
       <c r="B71" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72">
@@ -1417,7 +1318,7 @@
         <v>31</v>
       </c>
       <c r="B72" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="73">
@@ -1425,7 +1326,7 @@
         <v>31</v>
       </c>
       <c r="B73" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74">
@@ -1433,7 +1334,7 @@
         <v>32</v>
       </c>
       <c r="B74" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75">
@@ -1441,7 +1342,7 @@
         <v>32</v>
       </c>
       <c r="B75" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76">
@@ -1449,7 +1350,7 @@
         <v>32</v>
       </c>
       <c r="B76" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="77">
@@ -1457,7 +1358,7 @@
         <v>33</v>
       </c>
       <c r="B77" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78">
@@ -1465,7 +1366,7 @@
         <v>33</v>
       </c>
       <c r="B78" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="79">
@@ -1473,7 +1374,7 @@
         <v>33</v>
       </c>
       <c r="B79" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="80">
@@ -1481,7 +1382,7 @@
         <v>34</v>
       </c>
       <c r="B80" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81">
@@ -1489,7 +1390,7 @@
         <v>34</v>
       </c>
       <c r="B81" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82">
@@ -1497,7 +1398,7 @@
         <v>34</v>
       </c>
       <c r="B82" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83">
@@ -1505,7 +1406,7 @@
         <v>35</v>
       </c>
       <c r="B83" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84">
@@ -1513,7 +1414,7 @@
         <v>35</v>
       </c>
       <c r="B84" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85">
@@ -1521,7 +1422,7 @@
         <v>35</v>
       </c>
       <c r="B85" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="86">
@@ -1529,7 +1430,7 @@
         <v>36</v>
       </c>
       <c r="B86" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="87">
@@ -1537,7 +1438,7 @@
         <v>36</v>
       </c>
       <c r="B87" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="88">
@@ -1545,7 +1446,7 @@
         <v>36</v>
       </c>
       <c r="B88" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="89">
@@ -1553,7 +1454,7 @@
         <v>37</v>
       </c>
       <c r="B89" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90">
@@ -1561,7 +1462,7 @@
         <v>37</v>
       </c>
       <c r="B90" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="91">
@@ -1569,7 +1470,7 @@
         <v>37</v>
       </c>
       <c r="B91" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="92">
@@ -1577,7 +1478,7 @@
         <v>38</v>
       </c>
       <c r="B92" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93">
@@ -1585,7 +1486,7 @@
         <v>38</v>
       </c>
       <c r="B93" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94">
@@ -1593,7 +1494,7 @@
         <v>38</v>
       </c>
       <c r="B94" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95">
@@ -1601,7 +1502,7 @@
         <v>39</v>
       </c>
       <c r="B95" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96">
@@ -1609,7 +1510,7 @@
         <v>39</v>
       </c>
       <c r="B96" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="97">
@@ -1617,7 +1518,7 @@
         <v>39</v>
       </c>
       <c r="B97" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="98">
@@ -1625,7 +1526,7 @@
         <v>40</v>
       </c>
       <c r="B98" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99">
@@ -1633,7 +1534,7 @@
         <v>40</v>
       </c>
       <c r="B99" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="100">
@@ -1641,7 +1542,7 @@
         <v>40</v>
       </c>
       <c r="B100" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="101">
@@ -1649,7 +1550,7 @@
         <v>41</v>
       </c>
       <c r="B101" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102">
@@ -1657,7 +1558,7 @@
         <v>41</v>
       </c>
       <c r="B102" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="103">
@@ -1665,7 +1566,7 @@
         <v>41</v>
       </c>
       <c r="B103" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="104">
@@ -1673,7 +1574,7 @@
         <v>42</v>
       </c>
       <c r="B104" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="105">
@@ -1681,7 +1582,7 @@
         <v>42</v>
       </c>
       <c r="B105" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="106">
@@ -1689,7 +1590,7 @@
         <v>42</v>
       </c>
       <c r="B106" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="107">
@@ -1697,7 +1598,7 @@
         <v>43</v>
       </c>
       <c r="B107" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="108">
@@ -1705,7 +1606,7 @@
         <v>43</v>
       </c>
       <c r="B108" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="109">
@@ -1713,7 +1614,7 @@
         <v>43</v>
       </c>
       <c r="B109" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="110">
@@ -1721,7 +1622,7 @@
         <v>44</v>
       </c>
       <c r="B110" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="111">
@@ -1729,7 +1630,7 @@
         <v>44</v>
       </c>
       <c r="B111" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="112">
@@ -1737,7 +1638,7 @@
         <v>44</v>
       </c>
       <c r="B112" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="113">
@@ -1745,7 +1646,7 @@
         <v>45</v>
       </c>
       <c r="B113" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
     </row>
     <row r="114">
@@ -1753,7 +1654,7 @@
         <v>45</v>
       </c>
       <c r="B114" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="115">
@@ -1761,127 +1662,127 @@
         <v>45</v>
       </c>
       <c r="B115" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
+        <v>49</v>
+      </c>
+      <c r="B116" t="s">
         <v>46</v>
-      </c>
-      <c r="B116" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B117" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B118" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B119" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
+        <v>50</v>
+      </c>
+      <c r="B120" t="s">
         <v>47</v>
-      </c>
-      <c r="B120" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B121" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B122" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B123" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
+        <v>51</v>
+      </c>
+      <c r="B124" t="s">
         <v>48</v>
-      </c>
-      <c r="B124" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B125" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B126" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B127" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B128" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B129" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B130" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="131">
@@ -1889,7 +1790,7 @@
         <v>54</v>
       </c>
       <c r="B131" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="132">
@@ -1897,7 +1798,7 @@
         <v>54</v>
       </c>
       <c r="B132" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="133">
@@ -1905,7 +1806,7 @@
         <v>54</v>
       </c>
       <c r="B133" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="134">
@@ -1913,7 +1814,7 @@
         <v>55</v>
       </c>
       <c r="B134" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="135">
@@ -1921,7 +1822,7 @@
         <v>55</v>
       </c>
       <c r="B135" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="136">
@@ -1929,7 +1830,7 @@
         <v>55</v>
       </c>
       <c r="B136" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="137">
@@ -1937,7 +1838,7 @@
         <v>56</v>
       </c>
       <c r="B137" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="138">
@@ -1945,7 +1846,7 @@
         <v>56</v>
       </c>
       <c r="B138" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="139">
@@ -1953,7 +1854,7 @@
         <v>56</v>
       </c>
       <c r="B139" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="140">
@@ -1961,7 +1862,7 @@
         <v>57</v>
       </c>
       <c r="B140" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="141">
@@ -1969,7 +1870,7 @@
         <v>57</v>
       </c>
       <c r="B141" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="142">
@@ -1977,7 +1878,7 @@
         <v>57</v>
       </c>
       <c r="B142" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="143">
@@ -1985,7 +1886,7 @@
         <v>58</v>
       </c>
       <c r="B143" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="144">
@@ -1993,7 +1894,7 @@
         <v>58</v>
       </c>
       <c r="B144" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="145">
@@ -2001,7 +1902,7 @@
         <v>58</v>
       </c>
       <c r="B145" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="146">
@@ -2009,7 +1910,7 @@
         <v>59</v>
       </c>
       <c r="B146" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="147">
@@ -2017,7 +1918,7 @@
         <v>59</v>
       </c>
       <c r="B147" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="148">
@@ -2025,967 +1926,967 @@
         <v>59</v>
       </c>
       <c r="B148" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
+        <v>63</v>
+      </c>
+      <c r="B149" t="s">
         <v>60</v>
-      </c>
-      <c r="B149" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B150" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B151" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B152" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
+        <v>64</v>
+      </c>
+      <c r="B153" t="s">
         <v>61</v>
-      </c>
-      <c r="B153" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B154" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B155" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B156" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
+        <v>65</v>
+      </c>
+      <c r="B157" t="s">
         <v>62</v>
-      </c>
-      <c r="B157" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B158" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B159" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B160" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B161" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B162" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B163" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B164" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B165" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B166" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B167" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B168" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B169" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B170" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B171" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B172" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B173" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B174" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B175" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B176" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B177" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B178" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B179" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B180" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
+        <v>76</v>
+      </c>
+      <c r="B181" t="s">
         <v>73</v>
-      </c>
-      <c r="B181" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B182" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B183" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B184" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B185" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B186" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B187" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B188" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B189" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B190" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B191" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B192" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B193" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B194" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B195" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B196" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B197" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B198" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B199" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B200" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B201" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B202" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B203" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B204" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B205" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B206" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B207" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B208" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B209" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
+        <v>88</v>
+      </c>
+      <c r="B210" t="s">
         <v>83</v>
-      </c>
-      <c r="B210" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B211" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B212" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B213" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
+        <v>89</v>
+      </c>
+      <c r="B214" t="s">
         <v>84</v>
-      </c>
-      <c r="B214" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B215" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B216" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B217" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B218" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B219" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B220" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B221" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B222" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B223" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B224" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B225" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B226" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B227" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B228" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B229" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B230" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B231" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B232" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B233" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B234" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B235" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B236" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B237" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B238" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B239" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B240" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B241" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B242" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B243" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B244" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B245" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B246" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B247" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B248" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B249" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B250" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B251" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B252" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B253" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B254" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B255" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B256" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B257" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B258" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B259" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B260" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B261" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B262" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B263" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B264" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B265" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B266" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B267" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B268" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
     </row>
     <row r="269">
@@ -2993,7 +2894,7 @@
         <v>108</v>
       </c>
       <c r="B269" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="270">
@@ -3001,7 +2902,7 @@
         <v>108</v>
       </c>
       <c r="B270" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
     </row>
     <row r="271">
@@ -3009,7 +2910,7 @@
         <v>108</v>
       </c>
       <c r="B271" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
     </row>
     <row r="272">
@@ -3017,7 +2918,7 @@
         <v>109</v>
       </c>
       <c r="B272" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="273">
@@ -3025,7 +2926,7 @@
         <v>109</v>
       </c>
       <c r="B273" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
     </row>
     <row r="274">
@@ -3033,7 +2934,7 @@
         <v>109</v>
       </c>
       <c r="B274" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
     </row>
     <row r="275">
@@ -3041,7 +2942,7 @@
         <v>110</v>
       </c>
       <c r="B275" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="276">
@@ -3049,7 +2950,7 @@
         <v>110</v>
       </c>
       <c r="B276" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
     </row>
     <row r="277">
@@ -3057,7 +2958,7 @@
         <v>110</v>
       </c>
       <c r="B277" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
     </row>
     <row r="278">
@@ -3065,7 +2966,7 @@
         <v>111</v>
       </c>
       <c r="B278" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
     </row>
     <row r="279">
@@ -3073,7 +2974,7 @@
         <v>111</v>
       </c>
       <c r="B279" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
     </row>
     <row r="280">
@@ -3081,7 +2982,7 @@
         <v>111</v>
       </c>
       <c r="B280" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
     </row>
     <row r="281">
@@ -3089,7 +2990,7 @@
         <v>112</v>
       </c>
       <c r="B281" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
     </row>
     <row r="282">
@@ -3097,7 +2998,7 @@
         <v>112</v>
       </c>
       <c r="B282" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
     </row>
     <row r="283">
@@ -3105,7 +3006,7 @@
         <v>112</v>
       </c>
       <c r="B283" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
     </row>
     <row r="284">
@@ -3113,7 +3014,7 @@
         <v>113</v>
       </c>
       <c r="B284" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
     </row>
     <row r="285">
@@ -3121,7 +3022,7 @@
         <v>113</v>
       </c>
       <c r="B285" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
     </row>
     <row r="286">
@@ -3129,7 +3030,7 @@
         <v>113</v>
       </c>
       <c r="B286" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
     </row>
     <row r="287">
@@ -3137,7 +3038,7 @@
         <v>114</v>
       </c>
       <c r="B287" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
     </row>
     <row r="288">
@@ -3145,7 +3046,7 @@
         <v>114</v>
       </c>
       <c r="B288" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
     </row>
     <row r="289">
@@ -3153,7 +3054,7 @@
         <v>114</v>
       </c>
       <c r="B289" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
     </row>
     <row r="290">
@@ -3161,7 +3062,7 @@
         <v>115</v>
       </c>
       <c r="B290" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
     </row>
     <row r="291">
@@ -3169,7 +3070,7 @@
         <v>115</v>
       </c>
       <c r="B291" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
     </row>
     <row r="292">
@@ -3177,7 +3078,7 @@
         <v>115</v>
       </c>
       <c r="B292" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
     </row>
     <row r="293">
@@ -3185,7 +3086,7 @@
         <v>116</v>
       </c>
       <c r="B293" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
     </row>
     <row r="294">
@@ -3193,7 +3094,7 @@
         <v>116</v>
       </c>
       <c r="B294" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
     </row>
     <row r="295">
@@ -3201,7 +3102,7 @@
         <v>116</v>
       </c>
       <c r="B295" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
     </row>
     <row r="296">
@@ -3209,7 +3110,7 @@
         <v>117</v>
       </c>
       <c r="B296" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
     </row>
     <row r="297">
@@ -3217,7 +3118,7 @@
         <v>117</v>
       </c>
       <c r="B297" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
     </row>
     <row r="298">
@@ -3225,7 +3126,7 @@
         <v>117</v>
       </c>
       <c r="B298" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
     </row>
     <row r="299">
@@ -3233,7 +3134,7 @@
         <v>118</v>
       </c>
       <c r="B299" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
     </row>
     <row r="300">
@@ -3241,7 +3142,7 @@
         <v>118</v>
       </c>
       <c r="B300" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
     </row>
     <row r="301">
@@ -3249,7 +3150,7 @@
         <v>118</v>
       </c>
       <c r="B301" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
     </row>
     <row r="302">
@@ -3257,7 +3158,7 @@
         <v>119</v>
       </c>
       <c r="B302" t="s">
-        <v>89</v>
+        <v>3</v>
       </c>
     </row>
     <row r="303">
@@ -3265,7 +3166,7 @@
         <v>119</v>
       </c>
       <c r="B303" t="s">
-        <v>106</v>
+        <v>4</v>
       </c>
     </row>
     <row r="304">
@@ -3273,7 +3174,7 @@
         <v>119</v>
       </c>
       <c r="B304" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="305">
@@ -3281,7 +3182,7 @@
         <v>120</v>
       </c>
       <c r="B305" t="s">
-        <v>89</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -3289,7 +3190,7 @@
         <v>120</v>
       </c>
       <c r="B306" t="s">
-        <v>106</v>
+        <v>4</v>
       </c>
     </row>
     <row r="307">
@@ -3297,7 +3198,7 @@
         <v>120</v>
       </c>
       <c r="B307" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="308">
@@ -3305,7 +3206,7 @@
         <v>121</v>
       </c>
       <c r="B308" t="s">
-        <v>89</v>
+        <v>3</v>
       </c>
     </row>
     <row r="309">
@@ -3313,7 +3214,7 @@
         <v>121</v>
       </c>
       <c r="B309" t="s">
-        <v>106</v>
+        <v>4</v>
       </c>
     </row>
     <row r="310">
@@ -3321,7 +3222,7 @@
         <v>121</v>
       </c>
       <c r="B310" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="311">
@@ -3329,7 +3230,7 @@
         <v>122</v>
       </c>
       <c r="B311" t="s">
-        <v>89</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
@@ -3337,7 +3238,7 @@
         <v>122</v>
       </c>
       <c r="B312" t="s">
-        <v>106</v>
+        <v>4</v>
       </c>
     </row>
     <row r="313">
@@ -3345,7 +3246,7 @@
         <v>122</v>
       </c>
       <c r="B313" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="314">
@@ -3353,7 +3254,7 @@
         <v>123</v>
       </c>
       <c r="B314" t="s">
-        <v>89</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -3361,7 +3262,7 @@
         <v>123</v>
       </c>
       <c r="B315" t="s">
-        <v>106</v>
+        <v>4</v>
       </c>
     </row>
     <row r="316">
@@ -3369,7 +3270,7 @@
         <v>123</v>
       </c>
       <c r="B316" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="317">
@@ -3377,7 +3278,7 @@
         <v>124</v>
       </c>
       <c r="B317" t="s">
-        <v>89</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318">
@@ -3385,7 +3286,7 @@
         <v>124</v>
       </c>
       <c r="B318" t="s">
-        <v>106</v>
+        <v>4</v>
       </c>
     </row>
     <row r="319">
@@ -3393,7 +3294,7 @@
         <v>124</v>
       </c>
       <c r="B319" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="320">
@@ -3401,7 +3302,7 @@
         <v>125</v>
       </c>
       <c r="B320" t="s">
-        <v>89</v>
+        <v>3</v>
       </c>
     </row>
     <row r="321">
@@ -3409,7 +3310,7 @@
         <v>125</v>
       </c>
       <c r="B321" t="s">
-        <v>106</v>
+        <v>4</v>
       </c>
     </row>
     <row r="322">
@@ -3417,7 +3318,7 @@
         <v>125</v>
       </c>
       <c r="B322" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="323">
@@ -3425,7 +3326,7 @@
         <v>126</v>
       </c>
       <c r="B323" t="s">
-        <v>106</v>
+        <v>3</v>
       </c>
     </row>
     <row r="324">
@@ -3433,7 +3334,7 @@
         <v>126</v>
       </c>
       <c r="B324" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
     </row>
     <row r="325">
@@ -3441,7 +3342,7 @@
         <v>126</v>
       </c>
       <c r="B325" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="326">
@@ -3449,7 +3350,7 @@
         <v>127</v>
       </c>
       <c r="B326" t="s">
-        <v>106</v>
+        <v>3</v>
       </c>
     </row>
     <row r="327">
@@ -3457,7 +3358,7 @@
         <v>127</v>
       </c>
       <c r="B327" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
     </row>
     <row r="328">
@@ -3465,7 +3366,7 @@
         <v>127</v>
       </c>
       <c r="B328" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="329">
@@ -3473,7 +3374,7 @@
         <v>128</v>
       </c>
       <c r="B329" t="s">
-        <v>106</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330">
@@ -3481,7 +3382,7 @@
         <v>128</v>
       </c>
       <c r="B330" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
     </row>
     <row r="331">
@@ -3489,7 +3390,7 @@
         <v>128</v>
       </c>
       <c r="B331" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="332">
@@ -3497,7 +3398,7 @@
         <v>129</v>
       </c>
       <c r="B332" t="s">
-        <v>106</v>
+        <v>3</v>
       </c>
     </row>
     <row r="333">
@@ -3505,7 +3406,7 @@
         <v>129</v>
       </c>
       <c r="B333" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
     </row>
     <row r="334">
@@ -3513,7 +3414,7 @@
         <v>129</v>
       </c>
       <c r="B334" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="335">
@@ -3521,7 +3422,7 @@
         <v>130</v>
       </c>
       <c r="B335" t="s">
-        <v>106</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336">
@@ -3529,7 +3430,7 @@
         <v>130</v>
       </c>
       <c r="B336" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
     </row>
     <row r="337">
@@ -3537,7 +3438,7 @@
         <v>130</v>
       </c>
       <c r="B337" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="338">
@@ -3545,7 +3446,7 @@
         <v>131</v>
       </c>
       <c r="B338" t="s">
-        <v>106</v>
+        <v>3</v>
       </c>
     </row>
     <row r="339">
@@ -3553,7 +3454,7 @@
         <v>131</v>
       </c>
       <c r="B339" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
     </row>
     <row r="340">
@@ -3561,7 +3462,7 @@
         <v>131</v>
       </c>
       <c r="B340" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="341">
@@ -3569,7 +3470,7 @@
         <v>132</v>
       </c>
       <c r="B341" t="s">
-        <v>106</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -3577,7 +3478,7 @@
         <v>132</v>
       </c>
       <c r="B342" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
     </row>
     <row r="343">
@@ -3585,7 +3486,7 @@
         <v>132</v>
       </c>
       <c r="B343" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="344">
@@ -3593,7 +3494,7 @@
         <v>133</v>
       </c>
       <c r="B344" t="s">
-        <v>106</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -3601,7 +3502,7 @@
         <v>133</v>
       </c>
       <c r="B345" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
     </row>
     <row r="346">
@@ -3609,7 +3510,7 @@
         <v>133</v>
       </c>
       <c r="B346" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="347">
@@ -3617,7 +3518,7 @@
         <v>134</v>
       </c>
       <c r="B347" t="s">
-        <v>106</v>
+        <v>3</v>
       </c>
     </row>
     <row r="348">
@@ -3625,7 +3526,7 @@
         <v>134</v>
       </c>
       <c r="B348" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
     </row>
     <row r="349">
@@ -3633,798 +3534,6 @@
         <v>134</v>
       </c>
       <c r="B349" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="s">
-        <v>135</v>
-      </c>
-      <c r="B350" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="s">
-        <v>135</v>
-      </c>
-      <c r="B351" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="s">
-        <v>135</v>
-      </c>
-      <c r="B352" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="s">
-        <v>136</v>
-      </c>
-      <c r="B353" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="s">
-        <v>136</v>
-      </c>
-      <c r="B354" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="s">
-        <v>136</v>
-      </c>
-      <c r="B355" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="s">
-        <v>137</v>
-      </c>
-      <c r="B356" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="s">
-        <v>137</v>
-      </c>
-      <c r="B357" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="s">
-        <v>137</v>
-      </c>
-      <c r="B358" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="s">
-        <v>138</v>
-      </c>
-      <c r="B359" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="s">
-        <v>138</v>
-      </c>
-      <c r="B360" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="s">
-        <v>138</v>
-      </c>
-      <c r="B361" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="s">
-        <v>139</v>
-      </c>
-      <c r="B362" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="s">
-        <v>139</v>
-      </c>
-      <c r="B363" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="s">
-        <v>139</v>
-      </c>
-      <c r="B364" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="s">
-        <v>140</v>
-      </c>
-      <c r="B365" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="s">
-        <v>140</v>
-      </c>
-      <c r="B366" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="s">
-        <v>140</v>
-      </c>
-      <c r="B367" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="s">
-        <v>141</v>
-      </c>
-      <c r="B368" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="s">
-        <v>141</v>
-      </c>
-      <c r="B369" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="s">
-        <v>141</v>
-      </c>
-      <c r="B370" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="s">
-        <v>142</v>
-      </c>
-      <c r="B371" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="s">
-        <v>142</v>
-      </c>
-      <c r="B372" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="s">
-        <v>142</v>
-      </c>
-      <c r="B373" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="s">
-        <v>143</v>
-      </c>
-      <c r="B374" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="s">
-        <v>143</v>
-      </c>
-      <c r="B375" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="s">
-        <v>143</v>
-      </c>
-      <c r="B376" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="s">
-        <v>144</v>
-      </c>
-      <c r="B377" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="s">
-        <v>144</v>
-      </c>
-      <c r="B378" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="s">
-        <v>144</v>
-      </c>
-      <c r="B379" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="s">
-        <v>145</v>
-      </c>
-      <c r="B380" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="s">
-        <v>145</v>
-      </c>
-      <c r="B381" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="s">
-        <v>145</v>
-      </c>
-      <c r="B382" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="s">
-        <v>146</v>
-      </c>
-      <c r="B383" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="s">
-        <v>146</v>
-      </c>
-      <c r="B384" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="s">
-        <v>146</v>
-      </c>
-      <c r="B385" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="s">
-        <v>147</v>
-      </c>
-      <c r="B386" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="s">
-        <v>147</v>
-      </c>
-      <c r="B387" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="s">
-        <v>147</v>
-      </c>
-      <c r="B388" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="s">
-        <v>148</v>
-      </c>
-      <c r="B389" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="s">
-        <v>148</v>
-      </c>
-      <c r="B390" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="s">
-        <v>148</v>
-      </c>
-      <c r="B391" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="s">
-        <v>149</v>
-      </c>
-      <c r="B392" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="s">
-        <v>149</v>
-      </c>
-      <c r="B393" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="s">
-        <v>149</v>
-      </c>
-      <c r="B394" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="s">
-        <v>150</v>
-      </c>
-      <c r="B395" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="s">
-        <v>150</v>
-      </c>
-      <c r="B396" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="s">
-        <v>150</v>
-      </c>
-      <c r="B397" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="s">
-        <v>151</v>
-      </c>
-      <c r="B398" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="s">
-        <v>151</v>
-      </c>
-      <c r="B399" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="s">
-        <v>151</v>
-      </c>
-      <c r="B400" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="s">
-        <v>152</v>
-      </c>
-      <c r="B401" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" t="s">
-        <v>152</v>
-      </c>
-      <c r="B402" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="s">
-        <v>152</v>
-      </c>
-      <c r="B403" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" t="s">
-        <v>153</v>
-      </c>
-      <c r="B404" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="s">
-        <v>153</v>
-      </c>
-      <c r="B405" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="s">
-        <v>153</v>
-      </c>
-      <c r="B406" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="s">
-        <v>154</v>
-      </c>
-      <c r="B407" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" t="s">
-        <v>154</v>
-      </c>
-      <c r="B408" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="s">
-        <v>154</v>
-      </c>
-      <c r="B409" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="s">
-        <v>155</v>
-      </c>
-      <c r="B410" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="s">
-        <v>155</v>
-      </c>
-      <c r="B411" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="s">
-        <v>155</v>
-      </c>
-      <c r="B412" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="s">
-        <v>156</v>
-      </c>
-      <c r="B413" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="s">
-        <v>156</v>
-      </c>
-      <c r="B414" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="s">
-        <v>156</v>
-      </c>
-      <c r="B415" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="s">
-        <v>157</v>
-      </c>
-      <c r="B416" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="s">
-        <v>157</v>
-      </c>
-      <c r="B417" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="s">
-        <v>157</v>
-      </c>
-      <c r="B418" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="s">
-        <v>158</v>
-      </c>
-      <c r="B419" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="s">
-        <v>158</v>
-      </c>
-      <c r="B420" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="s">
-        <v>158</v>
-      </c>
-      <c r="B421" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" t="s">
-        <v>159</v>
-      </c>
-      <c r="B422" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" t="s">
-        <v>159</v>
-      </c>
-      <c r="B423" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" t="s">
-        <v>159</v>
-      </c>
-      <c r="B424" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="s">
-        <v>160</v>
-      </c>
-      <c r="B425" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="s">
-        <v>160</v>
-      </c>
-      <c r="B426" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="s">
-        <v>160</v>
-      </c>
-      <c r="B427" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="s">
-        <v>161</v>
-      </c>
-      <c r="B428" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="s">
-        <v>161</v>
-      </c>
-      <c r="B429" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="s">
-        <v>161</v>
-      </c>
-      <c r="B430" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="s">
-        <v>162</v>
-      </c>
-      <c r="B431" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" t="s">
-        <v>162</v>
-      </c>
-      <c r="B432" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="s">
-        <v>162</v>
-      </c>
-      <c r="B433" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="s">
-        <v>163</v>
-      </c>
-      <c r="B434" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="s">
-        <v>163</v>
-      </c>
-      <c r="B435" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="s">
-        <v>163</v>
-      </c>
-      <c r="B436" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="s">
-        <v>164</v>
-      </c>
-      <c r="B437" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="s">
-        <v>164</v>
-      </c>
-      <c r="B438" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="s">
-        <v>164</v>
-      </c>
-      <c r="B439" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" t="s">
-        <v>165</v>
-      </c>
-      <c r="B440" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="s">
-        <v>165</v>
-      </c>
-      <c r="B441" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" t="s">
-        <v>165</v>
-      </c>
-      <c r="B442" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="s">
-        <v>166</v>
-      </c>
-      <c r="B443" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="s">
-        <v>166</v>
-      </c>
-      <c r="B444" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" t="s">
-        <v>166</v>
-      </c>
-      <c r="B445" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" t="s">
-        <v>167</v>
-      </c>
-      <c r="B446" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" t="s">
-        <v>167</v>
-      </c>
-      <c r="B447" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" t="s">
-        <v>167</v>
-      </c>
-      <c r="B448" t="s">
         <v>5</v>
       </c>
     </row>
